--- a/documents/regitha-kb.xlsx
+++ b/documents/regitha-kb.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>context</t>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>CONTEXT</t>
   </si>
   <si>
     <t>Apa saja jenis pemasukan yang bisa dicatat?</t>
@@ -157,9 +157,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Manrope"/>
     </font>
     <font>
       <sz val="11.0"/>
